--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2942" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2521" uniqueCount="431">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -710,10 +710,10 @@
     <t>Only used if not implicit in code found in Condition.code. If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
   </si>
   <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -725,7 +725,183 @@
     <t>363698007</t>
   </si>
   <si>
-    <t>Condition.bodySite.id</t>
+    <t>Condition.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patient
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document)
+</t>
+  </si>
+  <si>
+    <t>Patient concerné</t>
+  </si>
+  <si>
+    <t>Indicates the patient or group who the condition record is associated with.</t>
+  </si>
+  <si>
+    <t>Group is typically used for veterinary or public health use cases.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>PID-3</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SBJ].role[classCode=PAT]</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>Condition.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Encounter created as part of</t>
+  </si>
+  <si>
+    <t>The Encounter during which this Condition was created or to which the creation of this record is tightly associated.</t>
+  </si>
+  <si>
+    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. This record indicates the encounter this particular record is associated with.  In the case of a "new" diagnosis reflecting ongoing/revised information about the condition, this might be distinct from the first encounter in which the underlying condition was first "known".</t>
+  </si>
+  <si>
+    <t>Event.context</t>
+  </si>
+  <si>
+    <t>PV1-19 (+PV1-54)</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]</t>
+  </si>
+  <si>
+    <t>dateTime
+AgePeriodRangestring</t>
+  </si>
+  <si>
+    <t>Estimated or actual date,  date-time, or age</t>
+  </si>
+  <si>
+    <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
+  </si>
+  <si>
+    <t>Age is generally used when the patient reports an age at which the Condition began to occur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>PRB-16</t>
+  </si>
+  <si>
+    <t>.effectiveTime.low or .inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="age at onset"].value</t>
+  </si>
+  <si>
+    <t>FiveWs.init</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetDateTime</t>
+  </si>
+  <si>
+    <t>onsetDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date de début du problème</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]</t>
+  </si>
+  <si>
+    <t>When in resolution/remission</t>
+  </si>
+  <si>
+    <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
+  </si>
+  <si>
+    <t>There is no explicit distinction between resolution and remission because in many cases the distinction is not clear. Age is generally used when the patient reports an age at which the Condition abated.  If there is no abatement element, it is unknown whether the condition has resolved or entered remission; applications and users should generally assume that the condition is still valid.  When abatementString exists, it implies the condition is abated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">con-4
+</t>
+  </si>
+  <si>
+    <t>.effectiveTime.high or .inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="age at remission"].value or .inboundRelationship[typeCode=SUBJ]source[classCode=CONC, moodCode=EVN].status=completed</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementDateTime</t>
+  </si>
+  <si>
+    <t>abatementDateTime</t>
+  </si>
+  <si>
+    <t>Date de fin du problème (si applicable)</t>
+  </si>
+  <si>
+    <t>Condition.recordedDate</t>
+  </si>
+  <si>
+    <t>Date record was first recorded</t>
+  </si>
+  <si>
+    <t>The recordedDate represents when this particular Condition record was created in the system, which is often a system-generated date.</t>
+  </si>
+  <si>
+    <t>REL-11</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>Condition.recorder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Who recorded the condition</t>
+  </si>
+  <si>
+    <t>Individual who recorded the record and takes responsibility for its content.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].role</t>
+  </si>
+  <si>
+    <t>FiveWs.author</t>
+  </si>
+  <si>
+    <t>Condition.recorder.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -744,7 +920,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Condition.bodySite.extension</t>
+    <t>Condition.recorder.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -757,365 +933,7 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Condition.bodySite.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Condition.bodySite.coding.id</t>
-  </si>
-  <si>
-    <t>Condition.bodySite.coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.bodySite.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Condition.bodySite.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Condition.bodySite.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Condition.bodySite.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Condition.bodySite.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Condition.bodySite.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Condition.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patient
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document)
-</t>
-  </si>
-  <si>
-    <t>Patient concerné</t>
-  </si>
-  <si>
-    <t>Indicates the patient or group who the condition record is associated with.</t>
-  </si>
-  <si>
-    <t>Group is typically used for veterinary or public health use cases.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>PID-3</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=SBJ].role[classCode=PAT]</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>Condition.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Encounter created as part of</t>
-  </si>
-  <si>
-    <t>The Encounter during which this Condition was created or to which the creation of this record is tightly associated.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. This record indicates the encounter this particular record is associated with.  In the case of a "new" diagnosis reflecting ongoing/revised information about the condition, this might be distinct from the first encounter in which the underlying condition was first "known".</t>
-  </si>
-  <si>
-    <t>Event.context</t>
-  </si>
-  <si>
-    <t>PV1-19 (+PV1-54)</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]</t>
-  </si>
-  <si>
-    <t>dateTime
-AgePeriodRangestring</t>
-  </si>
-  <si>
-    <t>Estimated or actual date,  date-time, or age</t>
-  </si>
-  <si>
-    <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
-  </si>
-  <si>
-    <t>Age is generally used when the patient reports an age at which the Condition began to occur.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>PRB-16</t>
-  </si>
-  <si>
-    <t>.effectiveTime.low or .inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="age at onset"].value</t>
-  </si>
-  <si>
-    <t>FiveWs.init</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetDateTime</t>
-  </si>
-  <si>
-    <t>onsetDateTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date de début du problème</t>
-  </si>
-  <si>
-    <t>Condition.abatement[x]</t>
-  </si>
-  <si>
-    <t>When in resolution/remission</t>
-  </si>
-  <si>
-    <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
-  </si>
-  <si>
-    <t>There is no explicit distinction between resolution and remission because in many cases the distinction is not clear. Age is generally used when the patient reports an age at which the Condition abated.  If there is no abatement element, it is unknown whether the condition has resolved or entered remission; applications and users should generally assume that the condition is still valid.  When abatementString exists, it implies the condition is abated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">con-4
-</t>
-  </si>
-  <si>
-    <t>.effectiveTime.high or .inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="age at remission"].value or .inboundRelationship[typeCode=SUBJ]source[classCode=CONC, moodCode=EVN].status=completed</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>Condition.abatement[x]:abatementDateTime</t>
-  </si>
-  <si>
-    <t>abatementDateTime</t>
-  </si>
-  <si>
-    <t>Date de fin du problème (si applicable)</t>
-  </si>
-  <si>
-    <t>Condition.recordedDate</t>
-  </si>
-  <si>
-    <t>Date record was first recorded</t>
-  </si>
-  <si>
-    <t>The recordedDate represents when this particular Condition record was created in the system, which is often a system-generated date.</t>
-  </si>
-  <si>
-    <t>REL-11</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Condition.recorder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who recorded the condition</t>
-  </si>
-  <si>
-    <t>Individual who recorded the record and takes responsibility for its content.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].role</t>
-  </si>
-  <si>
-    <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>Condition.recorder.id</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension</t>
   </si>
   <si>
     <t>Condition.recorder.extension:author</t>
@@ -1304,9 +1122,6 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -1873,7 +1688,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP77"/>
+  <dimension ref="A1:AP66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.93359375" customWidth="true" bestFit="true"/>
@@ -3843,7 +3658,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>215</v>
       </c>
@@ -3862,7 +3677,7 @@
         <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>79</v>
@@ -3906,11 +3721,9 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="Y17" t="s" s="2">
         <v>219</v>
       </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
         <v>220</v>
       </c>
@@ -3963,7 +3776,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>224</v>
       </c>
@@ -3972,35 +3785,37 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>79</v>
+        <v>225</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+      <c r="O18" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>79</v>
       </c>
@@ -4048,10 +3863,10 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>91</v>
@@ -4060,22 +3875,22 @@
         <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>79</v>
+        <v>230</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>79</v>
+        <v>231</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>79</v>
+        <v>233</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>79</v>
@@ -4083,21 +3898,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>79</v>
@@ -4106,19 +3921,19 @@
         <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>137</v>
+        <v>235</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>138</v>
+        <v>236</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>140</v>
+        <v>238</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4156,46 +3971,46 @@
         <v>79</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AF19" t="s" s="2">
-        <v>235</v>
-      </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>79</v>
+        <v>239</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>79</v>
+        <v>242</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>79</v>
@@ -4203,10 +4018,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4220,7 +4035,7 @@
         <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>79</v>
@@ -4229,20 +4044,18 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
@@ -4278,25 +4091,23 @@
         <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>79</v>
+        <v>249</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
@@ -4305,19 +4116,19 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>79</v>
+        <v>250</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>79</v>
@@ -4325,12 +4136,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>79</v>
       </c>
@@ -4348,18 +4161,20 @@
         <v>79</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4408,7 +4223,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4420,22 +4235,22 @@
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>79</v>
+        <v>250</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>79</v>
+        <v>251</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>79</v>
@@ -4443,24 +4258,24 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>79</v>
@@ -4469,16 +4284,16 @@
         <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>137</v>
+        <v>244</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>138</v>
+        <v>259</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>140</v>
+        <v>261</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4516,31 +4331,29 @@
         <v>79</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>79</v>
@@ -4552,23 +4365,25 @@
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>229</v>
+        <v>263</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>79</v>
       </c>
@@ -4580,29 +4395,27 @@
         <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>105</v>
+        <v>256</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
@@ -4611,7 +4424,7 @@
         <v>79</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>252</v>
+        <v>79</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>79</v>
@@ -4650,7 +4463,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4659,7 +4472,7 @@
         <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>103</v>
@@ -4671,13 +4484,13 @@
         <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>254</v>
+        <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>79</v>
@@ -4685,10 +4498,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4711,17 +4524,15 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4770,7 +4581,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4791,24 +4602,24 @@
         <v>79</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4822,7 +4633,7 @@
         <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>79</v>
@@ -4831,18 +4642,16 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>111</v>
+        <v>275</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>266</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
@@ -4890,7 +4699,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4911,13 +4720,13 @@
         <v>79</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>268</v>
+        <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>79</v>
@@ -4925,10 +4734,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4948,21 +4757,19 @@
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>225</v>
+        <v>281</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>273</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
       </c>
@@ -5010,7 +4817,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5022,7 +4829,7 @@
         <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>79</v>
@@ -5031,10 +4838,10 @@
         <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>275</v>
+        <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -5045,21 +4852,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>79</v>
@@ -5068,23 +4875,21 @@
         <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>278</v>
+        <v>137</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>279</v>
+        <v>138</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
@@ -5120,31 +4925,31 @@
         <v>79</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>79</v>
+        <v>249</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>79</v>
@@ -5153,7 +4958,7 @@
         <v>79</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>285</v>
@@ -5167,12 +4972,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="C28" s="2"/>
+      <c r="C28" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>79</v>
       </c>
@@ -5190,23 +4997,19 @@
         <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>225</v>
+        <v>293</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
@@ -5254,19 +5057,19 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>79</v>
@@ -5275,10 +5078,10 @@
         <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>292</v>
+        <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5287,46 +5090,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>295</v>
+        <v>79</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>299</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
       </c>
@@ -5374,10 +5175,10 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>91</v>
@@ -5386,22 +5187,22 @@
         <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>300</v>
+        <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>301</v>
+        <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>303</v>
+        <v>79</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
@@ -5409,10 +5210,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5420,10 +5221,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5432,20 +5233,18 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>305</v>
+        <v>137</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5482,46 +5281,46 @@
         <v>79</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>79</v>
+        <v>249</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>309</v>
+        <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>311</v>
+        <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>312</v>
+        <v>79</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>79</v>
@@ -5529,12 +5328,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>79</v>
       </c>
@@ -5546,26 +5347,24 @@
         <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>314</v>
+        <v>137</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5602,44 +5401,46 @@
         <v>79</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>321</v>
+        <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>322</v>
+        <v>79</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>79</v>
@@ -5647,14 +5448,12 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>79</v>
       </c>
@@ -5672,20 +5471,18 @@
         <v>79</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>325</v>
+        <v>281</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>326</v>
+        <v>282</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5734,7 +5531,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5746,22 +5543,22 @@
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>321</v>
+        <v>285</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>322</v>
+        <v>79</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>79</v>
@@ -5769,10 +5566,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5783,10 +5580,10 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>79</v>
@@ -5795,17 +5592,15 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>314</v>
+        <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>328</v>
+        <v>301</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5842,29 +5637,31 @@
         <v>79</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>327</v>
+        <v>290</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>331</v>
+        <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
@@ -5876,37 +5673,35 @@
         <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>332</v>
+        <v>79</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>333</v>
+        <v>79</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>79</v>
@@ -5915,16 +5710,16 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>325</v>
+        <v>105</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5932,7 +5727,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>79</v>
+        <v>304</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>79</v>
@@ -5974,19 +5769,19 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>331</v>
+        <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
@@ -5998,10 +5793,10 @@
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>332</v>
+        <v>134</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>333</v>
+        <v>79</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>79</v>
@@ -6009,10 +5804,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6032,16 +5827,16 @@
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>325</v>
+        <v>111</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6053,7 +5848,7 @@
         <v>79</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>79</v>
@@ -6068,13 +5863,11 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -6092,7 +5885,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6113,26 +5906,28 @@
         <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>340</v>
+        <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>341</v>
+        <v>134</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>342</v>
+        <v>79</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>79</v>
       </c>
@@ -6144,22 +5939,22 @@
         <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>344</v>
+        <v>137</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>346</v>
+        <v>302</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6210,19 +6005,19 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>343</v>
+        <v>290</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>79</v>
@@ -6234,10 +6029,10 @@
         <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>347</v>
+        <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>348</v>
+        <v>79</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>79</v>
@@ -6245,10 +6040,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>349</v>
+        <v>325</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>349</v>
+        <v>306</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6271,13 +6066,13 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>225</v>
+        <v>281</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>226</v>
+        <v>282</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>227</v>
+        <v>283</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6328,7 +6123,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>228</v>
+        <v>284</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6352,7 +6147,7 @@
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>229</v>
+        <v>285</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6363,21 +6158,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>308</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>79</v>
@@ -6392,14 +6187,12 @@
         <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>138</v>
+        <v>301</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6436,19 +6229,19 @@
         <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>233</v>
+        <v>289</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>235</v>
+        <v>290</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6472,7 +6265,7 @@
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>229</v>
+        <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6483,20 +6276,18 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>91</v>
@@ -6511,22 +6302,24 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>353</v>
+        <v>105</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>79</v>
@@ -6568,19 +6361,19 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>235</v>
+        <v>314</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>79</v>
@@ -6592,7 +6385,7 @@
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6603,10 +6396,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>356</v>
+        <v>328</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6629,13 +6422,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>225</v>
+        <v>158</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>226</v>
+        <v>317</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>227</v>
+        <v>318</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6686,7 +6479,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>228</v>
+        <v>321</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6698,7 +6491,7 @@
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
@@ -6710,7 +6503,7 @@
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>229</v>
+        <v>134</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6721,21 +6514,23 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="D41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>360</v>
+        <v>91</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -6750,10 +6545,10 @@
         <v>137</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>361</v>
+        <v>301</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>362</v>
+        <v>302</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6792,19 +6587,19 @@
         <v>79</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>235</v>
+        <v>290</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6839,20 +6634,18 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>363</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>91</v>
@@ -6867,13 +6660,13 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>137</v>
+        <v>281</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>361</v>
+        <v>282</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>362</v>
+        <v>283</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6924,19 +6717,19 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>235</v>
+        <v>284</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
@@ -6948,7 +6741,7 @@
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -6959,10 +6752,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>365</v>
+        <v>332</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>366</v>
+        <v>308</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6973,7 +6766,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>79</v>
@@ -6985,13 +6778,13 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>225</v>
+        <v>137</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>226</v>
+        <v>301</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>227</v>
+        <v>302</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7030,31 +6823,31 @@
         <v>79</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>79</v>
+        <v>249</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>228</v>
+        <v>290</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>79</v>
@@ -7066,7 +6859,7 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>229</v>
+        <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -7077,10 +6870,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>367</v>
+        <v>333</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>368</v>
+        <v>310</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7088,10 +6881,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -7103,22 +6896,24 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>361</v>
+        <v>311</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>79</v>
+        <v>330</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>79</v>
@@ -7148,31 +6943,31 @@
         <v>79</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>235</v>
+        <v>314</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>79</v>
@@ -7184,7 +6979,7 @@
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7195,10 +6990,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>369</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>370</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7206,7 +7001,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>91</v>
@@ -7221,24 +7016,22 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>105</v>
+        <v>335</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>364</v>
+        <v>79</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>79</v>
@@ -7280,10 +7073,10 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>374</v>
+        <v>321</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>91</v>
@@ -7292,7 +7085,7 @@
         <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>79</v>
@@ -7315,10 +7108,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>375</v>
+        <v>336</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>376</v>
+        <v>337</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7326,7 +7119,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>91</v>
@@ -7341,25 +7134,27 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>377</v>
+        <v>311</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>79</v>
+        <v>338</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>379</v>
+        <v>79</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>79</v>
@@ -7374,11 +7169,13 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>380</v>
+        <v>79</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -7396,10 +7193,10 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>381</v>
+        <v>314</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>91</v>
@@ -7408,7 +7205,7 @@
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
@@ -7431,14 +7228,12 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>382</v>
+        <v>339</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7447,7 +7242,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7459,13 +7254,13 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>137</v>
+        <v>341</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>384</v>
+        <v>317</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>362</v>
+        <v>318</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7516,19 +7311,19 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>235</v>
+        <v>321</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
@@ -7540,7 +7335,7 @@
         <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7551,10 +7346,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7574,18 +7369,20 @@
         <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>225</v>
+        <v>281</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>226</v>
+        <v>343</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7634,7 +7431,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>228</v>
+        <v>346</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7643,10 +7440,10 @@
         <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>79</v>
+        <v>347</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
@@ -7658,7 +7455,7 @@
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>229</v>
+        <v>134</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7669,10 +7466,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>386</v>
+        <v>348</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7683,7 +7480,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>79</v>
@@ -7692,18 +7489,20 @@
         <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7728,43 +7527,43 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>79</v>
+        <v>353</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>235</v>
+        <v>354</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
@@ -7776,7 +7575,7 @@
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7787,10 +7586,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>387</v>
+        <v>355</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7798,7 +7597,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>91</v>
@@ -7810,19 +7609,19 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7830,7 +7629,7 @@
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>383</v>
+        <v>79</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>79</v>
@@ -7872,10 +7671,10 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>91</v>
@@ -7884,7 +7683,7 @@
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
@@ -7896,7 +7695,7 @@
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>134</v>
+        <v>360</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7907,10 +7706,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>388</v>
+        <v>361</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7930,18 +7729,20 @@
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>158</v>
+        <v>281</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -7990,7 +7791,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8025,20 +7826,18 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>366</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>91</v>
@@ -8050,16 +7849,16 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>137</v>
+        <v>275</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8110,19 +7909,19 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>235</v>
+        <v>366</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
@@ -8131,13 +7930,13 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>79</v>
+        <v>369</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -8145,10 +7944,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8159,7 +7958,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -8171,13 +7970,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>225</v>
+        <v>373</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>226</v>
+        <v>374</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>227</v>
+        <v>375</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8228,19 +8027,19 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>228</v>
+        <v>372</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>79</v>
+        <v>376</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
@@ -8252,7 +8051,7 @@
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>229</v>
+        <v>377</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8263,10 +8062,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8277,7 +8076,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>79</v>
@@ -8289,13 +8088,13 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>137</v>
+        <v>281</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>361</v>
+        <v>282</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>362</v>
+        <v>283</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8334,31 +8133,31 @@
         <v>79</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>235</v>
+        <v>284</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
@@ -8370,7 +8169,7 @@
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8381,21 +8180,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
@@ -8407,16 +8206,16 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>371</v>
+        <v>138</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>372</v>
+        <v>287</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>373</v>
+        <v>140</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8424,7 +8223,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>390</v>
+        <v>79</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>79</v>
@@ -8466,19 +8265,19 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>374</v>
+        <v>290</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
@@ -8490,7 +8289,7 @@
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>134</v>
+        <v>285</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8501,42 +8300,46 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>395</v>
+        <v>137</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
       </c>
@@ -8584,19 +8387,19 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
@@ -8617,12 +8420,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8630,13 +8433,13 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>79</v>
@@ -8645,24 +8448,22 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>105</v>
+        <v>158</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>398</v>
+        <v>79</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>79</v>
@@ -8680,13 +8481,11 @@
         <v>79</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>79</v>
+        <v>388</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>79</v>
@@ -8704,31 +8503,31 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>79</v>
+        <v>389</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>134</v>
+        <v>212</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8739,10 +8538,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8753,7 +8552,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -8765,13 +8564,13 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8822,16 +8621,16 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>79</v>
+        <v>389</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>103</v>
@@ -8846,7 +8645,7 @@
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>134</v>
+        <v>395</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -8857,10 +8656,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8880,20 +8679,18 @@
         <v>79</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>225</v>
+        <v>158</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>79</v>
@@ -8918,13 +8715,13 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>79</v>
+        <v>399</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>79</v>
+        <v>400</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -8942,7 +8739,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8951,7 +8748,7 @@
         <v>91</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>407</v>
+        <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>103</v>
@@ -8966,7 +8763,7 @@
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>134</v>
+        <v>401</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -8977,10 +8774,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8991,7 +8788,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>79</v>
@@ -9000,19 +8797,19 @@
         <v>79</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>105</v>
+        <v>373</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9038,13 +8835,13 @@
         <v>79</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>412</v>
+        <v>79</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>413</v>
+        <v>79</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>414</v>
+        <v>79</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>79</v>
@@ -9062,19 +8859,19 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>103</v>
+        <v>406</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>79</v>
@@ -9086,7 +8883,7 @@
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>134</v>
+        <v>407</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -9097,10 +8894,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9120,20 +8917,18 @@
         <v>79</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>149</v>
+        <v>281</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>417</v>
+        <v>282</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9182,7 +8977,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9194,7 +8989,7 @@
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>79</v>
@@ -9206,7 +9001,7 @@
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>421</v>
+        <v>285</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9217,21 +9012,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>79</v>
@@ -9240,19 +9035,19 @@
         <v>79</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>225</v>
+        <v>137</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>423</v>
+        <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>424</v>
+        <v>287</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>425</v>
+        <v>140</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9302,19 +9097,19 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>426</v>
+        <v>290</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>79</v>
@@ -9326,7 +9121,7 @@
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>134</v>
+        <v>285</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9337,42 +9132,46 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>344</v>
+        <v>137</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>428</v>
+        <v>382</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
       </c>
@@ -9420,19 +9219,19 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>427</v>
+        <v>384</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>79</v>
@@ -9441,13 +9240,13 @@
         <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>430</v>
+        <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>431</v>
+        <v>134</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>432</v>
+        <v>79</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>79</v>
@@ -9455,10 +9254,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9478,16 +9277,16 @@
         <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>434</v>
+        <v>158</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>436</v>
+        <v>413</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9514,13 +9313,13 @@
         <v>79</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>79</v>
+        <v>414</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>79</v>
+        <v>415</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>79</v>
@@ -9538,7 +9337,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9547,25 +9346,25 @@
         <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>437</v>
+        <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>79</v>
+        <v>417</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>79</v>
+        <v>187</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>79</v>
+        <v>419</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>79</v>
@@ -9573,10 +9372,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9587,7 +9386,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>79</v>
@@ -9596,16 +9395,16 @@
         <v>79</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>225</v>
+        <v>421</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>226</v>
+        <v>422</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>227</v>
+        <v>423</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9656,19 +9455,19 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>228</v>
+        <v>420</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>79</v>
@@ -9680,35 +9479,35 @@
         <v>79</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>229</v>
+        <v>395</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>79</v>
+        <v>419</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>79</v>
@@ -9717,17 +9516,15 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>137</v>
+        <v>425</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>138</v>
+        <v>426</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -9776,7 +9573,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>235</v>
+        <v>424</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9788,1337 +9585,29 @@
         <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>79</v>
+        <v>429</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>229</v>
+        <v>430</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Y68" s="2"/>
-      <c r="Z68" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP77" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP77">
+  <autoFilter ref="A1:AP66">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11128,7 +9617,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI76">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
